--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,28 +391,60 @@
           <t>upper_q_visits_per_year</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.47</v>
+        <v>22.9</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>433</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>24.53</v>
+        <v>23.34</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="H2">
+        <v>18133</v>
+      </c>
+      <c r="I2">
+        <v>0.17</v>
+      </c>
+      <c r="J2">
+        <v>22.56</v>
+      </c>
+      <c r="K2">
+        <v>23.24</v>
       </c>
     </row>
   </sheetData>
@@ -422,7 +454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -461,28 +493,60 @@
           <t>upper_q_visits_per_year</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.9</v>
+        <v>23.54</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>433</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>24.48</v>
+        <v>23.35</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="H2">
+        <v>17639</v>
+      </c>
+      <c r="I2">
+        <v>0.18</v>
+      </c>
+      <c r="J2">
+        <v>23.2</v>
+      </c>
+      <c r="K2">
+        <v>23.89</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>22.9</v>
+        <v>19.36</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>401</v>
       </c>
       <c r="D2">
-        <v>23.34</v>
+        <v>22.1</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H2">
         <v>18133</v>
       </c>
       <c r="I2">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="J2">
-        <v>22.56</v>
+        <v>19.04</v>
       </c>
       <c r="K2">
-        <v>23.24</v>
+        <v>19.68</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23.54</v>
+        <v>20.28</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -525,28 +525,28 @@
         <v>401</v>
       </c>
       <c r="D2">
-        <v>23.35</v>
+        <v>22.2</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H2">
-        <v>17639</v>
+        <v>17311</v>
       </c>
       <c r="I2">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J2">
-        <v>23.2</v>
+        <v>19.95</v>
       </c>
       <c r="K2">
-        <v>23.89</v>
+        <v>20.61</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>19.36</v>
+        <v>21.14</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>401</v>
       </c>
       <c r="D2">
-        <v>22.1</v>
+        <v>22.26</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2">
-        <v>18133</v>
+        <v>23106</v>
       </c>
       <c r="I2">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="J2">
-        <v>19.04</v>
+        <v>20.85</v>
       </c>
       <c r="K2">
-        <v>19.68</v>
+        <v>21.43</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>20.28</v>
+        <v>21.8</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -525,28 +525,28 @@
         <v>401</v>
       </c>
       <c r="D2">
-        <v>22.2</v>
+        <v>22.29</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="I2">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J2">
-        <v>19.95</v>
+        <v>21.51</v>
       </c>
       <c r="K2">
-        <v>20.61</v>
+        <v>22.09</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>21.14</v>
+        <v>47.09</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>401</v>
+        <v>1422</v>
       </c>
       <c r="D2">
-        <v>22.26</v>
+        <v>48.77</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="H2">
-        <v>23106</v>
+        <v>23007</v>
       </c>
       <c r="I2">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="J2">
-        <v>20.85</v>
+        <v>46.46</v>
       </c>
       <c r="K2">
-        <v>21.43</v>
+        <v>47.72</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>21.8</v>
+        <v>29.84</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>401</v>
+        <v>671</v>
       </c>
       <c r="D2">
-        <v>22.29</v>
+        <v>32.75</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H2">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="I2">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="J2">
-        <v>21.51</v>
+        <v>29.41</v>
       </c>
       <c r="K2">
-        <v>22.09</v>
+        <v>30.26</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Unadjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>47.09</v>
+        <v>21.14</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1422</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>48.77</v>
+        <v>22.26</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="H2">
-        <v>23007</v>
+        <v>23106</v>
       </c>
       <c r="I2">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="J2">
-        <v>46.46</v>
+        <v>20.85</v>
       </c>
       <c r="K2">
-        <v>47.72</v>
+        <v>21.43</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>29.84</v>
+        <v>21.8</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>671</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>32.75</v>
+        <v>22.29</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>22462</v>
+        <v>22407</v>
       </c>
       <c r="I2">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="J2">
-        <v>29.41</v>
+        <v>21.51</v>
       </c>
       <c r="K2">
-        <v>30.26</v>
+        <v>22.09</v>
       </c>
     </row>
   </sheetData>
